--- a/02_DIA_inicio_2026_analisis_assets/rbd_9611_escuela-basica-tupahue_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9611_escuela-basica-tupahue_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AED408A9-3BA6-4211-BFD0-EFB99111BDAC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4162C90-5AA0-49E0-965E-515B5E7F3FB8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2BA4DBE-FB26-47C1-A140-62E56328A642}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD5F65AA-5237-4768-A43C-73009A1AC44C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E0A291F-F305-4079-BCA9-D1215361C78A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A72DBCA-4948-4380-A7EB-809717B21B59}"/>
 </file>